--- a/dati/CONSEGNE/CONSEGNE_14-04-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_14-04-2026/punti_consegna.xlsx
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>45.4256448</v>
+        <v>45.67898086660827</v>
       </c>
       <c r="J32" t="n">
-        <v>12.0713225</v>
+        <v>11.50217561555479</v>
       </c>
     </row>
     <row r="33">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>45.4256448</v>
+        <v>45.67898086660827</v>
       </c>
       <c r="J52" t="n">
-        <v>12.0713225</v>
+        <v>11.50217561555479</v>
       </c>
     </row>
     <row r="53">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>45.7035986</v>
+        <v>45.67425448117051</v>
       </c>
       <c r="J88" t="n">
-        <v>11.5703868</v>
+        <v>11.91887373432651</v>
       </c>
     </row>
     <row r="89">
